--- a/artfynd/A 42427-2026 artfynd.xlsx
+++ b/artfynd/A 42427-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>112181998</v>
+        <v>137442543</v>
       </c>
       <c r="B3" t="n">
-        <v>93209</v>
+        <v>93485</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -802,41 +802,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Banker</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sorsele, Ly lm</t>
+          <t>Erik-Ersmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612860</v>
+        <v>613373</v>
       </c>
       <c r="R3" t="n">
-        <v>7271422</v>
+        <v>7271621</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +856,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-09-07</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -885,74 +886,69 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Mimmi Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112181998</t>
+          <t>https://artportalen.se/Sighting/137442543</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123970436</v>
+        <v>112181998</v>
       </c>
       <c r="B4" t="n">
-        <v>56925</v>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100045</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Sångsvan</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Cygnus cygnus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Granberget, Njunnesvare, Ly lm</t>
+          <t>Sorsele, Ly lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>613004</v>
+        <v>612860</v>
       </c>
       <c r="R4" t="n">
-        <v>7271457</v>
+        <v>7271422</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -976,22 +972,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2023-09-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:26</t>
+          <t>2023-09-07</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,76 +997,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kerstin Sundberg-Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kerstin Sundberg-Persson</t>
+          <t>Mimmi Persson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123970436</t>
+          <t>https://artportalen.se/Sighting/112181998</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>57577962</v>
+        <v>137440948</v>
       </c>
       <c r="B5" t="n">
-        <v>57899</v>
+        <v>79535</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100067</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Granberget, Njunnesvare, Ly lm</t>
+          <t>Forsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>613004</v>
+        <v>613503</v>
       </c>
       <c r="R5" t="n">
-        <v>7271457</v>
+        <v>7271355</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1099,22 +1079,27 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2016-03-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2016-03-10</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På flera träd</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,27 +1114,27 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Simon  Paulin</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Simon  Paulin</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/57577962</t>
+          <t>https://artportalen.se/Sighting/137440948</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>20278947</v>
+        <v>137440998</v>
       </c>
       <c r="B6" t="n">
-        <v>57791</v>
+        <v>79535</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,41 +1142,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102620</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hökuggla</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Surnia ulula</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Granberget, Njunnesvare, Ly lm</t>
+          <t>Forsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>613004</v>
+        <v>613500</v>
       </c>
       <c r="R6" t="n">
-        <v>7271457</v>
+        <v>7271392</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1215,27 +1196,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2005-01-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2005-01-21</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:05</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Njunnesvare sydsluttning, nära Tärnavgn</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,27 +1226,27 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Bernt-Erik Nordenström</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/20278947</t>
+          <t>https://artportalen.se/Sighting/137440998</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134362017</v>
+        <v>137441461</v>
       </c>
       <c r="B7" t="n">
-        <v>58563</v>
+        <v>79292</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,49 +1254,40 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102987</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Granberget, Njunnesvare, Ly lm</t>
+          <t>Forsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>613004</v>
+        <v>613480</v>
       </c>
       <c r="R7" t="n">
-        <v>7271457</v>
+        <v>7271463</v>
       </c>
       <c r="S7" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,12 +1311,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>10:33</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,33 +1335,34 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Oskar Karsikko</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Oskar Karsikko</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134362017</t>
+          <t>https://artportalen.se/Sighting/137441461</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134362005</v>
+        <v>137441805</v>
       </c>
       <c r="B8" t="n">
-        <v>58260</v>
+        <v>79292</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1392,49 +1370,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103012</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Granberget, Njunnesvare, Ly lm</t>
+          <t>Forsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>613004</v>
+        <v>613438</v>
       </c>
       <c r="R8" t="n">
-        <v>7271457</v>
+        <v>7271534</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1458,12 +1424,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1478,27 +1454,27 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Oskar Karsikko</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Oskar Karsikko</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134362005</t>
+          <t>https://artportalen.se/Sighting/137441805</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123970437</v>
+        <v>137442130</v>
       </c>
       <c r="B9" t="n">
-        <v>58114</v>
+        <v>79292</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1506,42 +1482,40 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Granberget, Njunnesvare, Ly lm</t>
+          <t>Forsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>613004</v>
+        <v>613404</v>
       </c>
       <c r="R9" t="n">
-        <v>7271457</v>
+        <v>7271534</v>
       </c>
       <c r="S9" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1565,22 +1539,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-11</t>
+          <t>2026-10-25</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,83 +1563,72 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kerstin Sundberg-Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kerstin Sundberg-Persson</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123970437</t>
+          <t>https://artportalen.se/Sighting/137442130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134362012</v>
+        <v>137441266</v>
       </c>
       <c r="B10" t="n">
-        <v>58658</v>
+        <v>80650</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103044</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Granberget, Njunnesvare, Ly lm</t>
+          <t>Forsmyran, Ly lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>613004</v>
+        <v>613513</v>
       </c>
       <c r="R10" t="n">
-        <v>7271457</v>
+        <v>7271355</v>
       </c>
       <c r="S10" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,12 +1652,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1709,18 +1682,1850 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Oskar Karsikko</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Oskar Karsikko</t>
+          <t>Ulrika Karlsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137441266</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>137440955</v>
+      </c>
+      <c r="B11" t="n">
+        <v>80655</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Forsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>613500</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7271392</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137440955</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>137441289</v>
+      </c>
+      <c r="B12" t="n">
+        <v>80662</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6464</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Luddlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Nephroma resupinatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Forsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>613513</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7271355</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>10:23</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441289</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>123970436</v>
+      </c>
+      <c r="B13" t="n">
+        <v>56925</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>100045</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Sångsvan</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cygnus cygnus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Granberget, Njunnesvare, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>613004</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7271457</v>
+      </c>
+      <c r="S13" t="n">
+        <v>13</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kerstin Sundberg-Persson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kerstin Sundberg-Persson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970436</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>57577962</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100067</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Havsörn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Haliaeetus albicilla</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Granberget, Njunnesvare, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>613004</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7271457</v>
+      </c>
+      <c r="S14" t="n">
+        <v>13</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2016-03-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2016-03-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Simon  Paulin</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Simon  Paulin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/57577962</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>20278947</v>
+      </c>
+      <c r="B15" t="n">
+        <v>57791</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102620</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Hökuggla</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Surnia ulula</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Granberget, Njunnesvare, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>613004</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7271457</v>
+      </c>
+      <c r="S15" t="n">
+        <v>13</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2005-01-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2005-01-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Njunnesvare sydsluttning, nära Tärnavgn</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Bernt-Erik Nordenström</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Bernt-Erik Nordenström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/20278947</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134362017</v>
+      </c>
+      <c r="B16" t="n">
+        <v>58563</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>102987</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Sädesärla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Motacilla alba</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Granberget, Njunnesvare, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>613004</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7271457</v>
+      </c>
+      <c r="S16" t="n">
+        <v>13</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Oskar Karsikko</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Oskar Karsikko</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362017</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134362005</v>
+      </c>
+      <c r="B17" t="n">
+        <v>58260</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>103012</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grönsångare</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Phylloscopus sibilatrix</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Granberget, Njunnesvare, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>613004</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7271457</v>
+      </c>
+      <c r="S17" t="n">
+        <v>13</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Oskar Karsikko</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Oskar Karsikko</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134362005</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123970437</v>
+      </c>
+      <c r="B18" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Granberget, Njunnesvare, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>613004</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7271457</v>
+      </c>
+      <c r="S18" t="n">
+        <v>13</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kerstin Sundberg-Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kerstin Sundberg-Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123970437</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134362012</v>
+      </c>
+      <c r="B19" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Granberget, Njunnesvare, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>613004</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7271457</v>
+      </c>
+      <c r="S19" t="n">
+        <v>13</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-13</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Oskar Karsikko</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Oskar Karsikko</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/134362012</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>137441667</v>
+      </c>
+      <c r="B20" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Forsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>613470</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7271480</v>
+      </c>
+      <c r="S20" t="n">
+        <v>1</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>10:43</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441667</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137442863</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Erik-Ersmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>613287</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7271687</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:45</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442863</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137442928</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98302</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Erik-Ersmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>613287</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7271688</v>
+      </c>
+      <c r="S22" t="n">
+        <v>1</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442928</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>137440825</v>
+      </c>
+      <c r="B23" t="n">
+        <v>104161</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Forsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>613541</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7271319</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137440825</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>137441142</v>
+      </c>
+      <c r="B24" t="n">
+        <v>104161</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Forsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>613500</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7271392</v>
+      </c>
+      <c r="S24" t="n">
+        <v>1</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:13</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137441142</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>137442264</v>
+      </c>
+      <c r="B25" t="n">
+        <v>104161</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Forsmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>613368</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7271584</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442264</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>137442386</v>
+      </c>
+      <c r="B26" t="n">
+        <v>104161</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>223284</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Sälg</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Erik-Ersmyran, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>613373</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7271621</v>
+      </c>
+      <c r="S26" t="n">
+        <v>1</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Sorsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Ulrika Karlsson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137442386</t>
         </is>
       </c>
     </row>
@@ -1735,6 +3540,22 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 42427-2026 artfynd.xlsx
+++ b/artfynd/A 42427-2026 artfynd.xlsx
@@ -794,7 +794,7 @@
         <v>137442543</v>
       </c>
       <c r="B3" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>137440948</v>
       </c>
       <c r="B5" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1134,7 +1134,7 @@
         <v>137440998</v>
       </c>
       <c r="B6" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1246,7 +1246,7 @@
         <v>137441461</v>
       </c>
       <c r="B7" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>137441805</v>
       </c>
       <c r="B8" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>137442130</v>
       </c>
       <c r="B9" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         <v>137441266</v>
       </c>
       <c r="B10" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1702,7 +1702,7 @@
         <v>137440955</v>
       </c>
       <c r="B11" t="n">
-        <v>80655</v>
+        <v>80659</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1814,7 +1814,7 @@
         <v>137441289</v>
       </c>
       <c r="B12" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>137441667</v>
       </c>
       <c r="B20" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         <v>137442863</v>
       </c>
       <c r="B21" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2974,7 +2974,7 @@
         <v>137442928</v>
       </c>
       <c r="B22" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>137440825</v>
       </c>
       <c r="B23" t="n">
-        <v>104161</v>
+        <v>104166</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>137441142</v>
       </c>
       <c r="B24" t="n">
-        <v>104161</v>
+        <v>104166</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3310,7 +3310,7 @@
         <v>137442264</v>
       </c>
       <c r="B25" t="n">
-        <v>104161</v>
+        <v>104166</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3422,7 +3422,7 @@
         <v>137442386</v>
       </c>
       <c r="B26" t="n">
-        <v>104161</v>
+        <v>104166</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
